--- a/2020.HK.xlsx
+++ b/2020.HK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734786B0-AE32-4BEC-AC14-AE2E7DF794B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13C1D0D-6D4B-4D61-A784-457070D150FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{A24C8550-AABC-4E33-81F8-E1B227287154}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{A24C8550-AABC-4E33-81F8-E1B227287154}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="89">
   <si>
     <t>Anta Sports Prouducts</t>
   </si>
@@ -300,7 +300,10 @@
     <t>Employee- Count</t>
   </si>
   <si>
-    <t>Q225</t>
+    <t>FY25</t>
+  </si>
+  <si>
+    <t>Q425</t>
   </si>
 </sst>
 </file>
@@ -312,13 +315,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -500,41 +509,44 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -895,7 +907,7 @@
         <v>78</v>
       </c>
       <c r="H2" s="3">
-        <v>101.6</v>
+        <v>80.55</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -904,7 +916,7 @@
       </c>
       <c r="H3" s="3">
         <f>+H2*H10</f>
-        <v>94.488</v>
+        <v>74.911500000000004</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -912,10 +924,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="4">
-        <v>2808.377</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>87</v>
+        <v>2780.4319999999998</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -927,7 +939,7 @@
       </c>
       <c r="H5" s="3">
         <f>+H3*H4</f>
-        <v>265357.92597599997</v>
+        <v>208286.331768</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -938,11 +950,11 @@
         <v>3</v>
       </c>
       <c r="H6" s="3">
-        <f>9656+18543+987+2958</f>
-        <v>32144</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>87</v>
+        <f>12181+24275</f>
+        <v>36456</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -950,11 +962,11 @@
         <v>4</v>
       </c>
       <c r="H7" s="3">
-        <f>11889+12151</f>
-        <v>24040</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>87</v>
+        <f>11532+11770</f>
+        <v>23302</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -974,7 +986,7 @@
       </c>
       <c r="H8" s="3">
         <f>+H5-H6+H7</f>
-        <v>257253.92597599997</v>
+        <v>195132.331768</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -1116,6 +1128,9 @@
       <c r="Q2" s="5" t="s">
         <v>77</v>
       </c>
+      <c r="R2" s="29" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="3" spans="1:80" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -1142,7 +1157,9 @@
       <c r="I3" s="4">
         <v>7187</v>
       </c>
-      <c r="J3" s="4"/>
+      <c r="J3" s="4">
+        <v>7203</v>
+      </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
@@ -1158,7 +1175,9 @@
       <c r="Q3" s="4">
         <v>7135</v>
       </c>
-      <c r="R3" s="4"/>
+      <c r="R3" s="4">
+        <v>7203</v>
+      </c>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
@@ -1247,7 +1266,9 @@
       <c r="I4" s="4">
         <v>2722</v>
       </c>
-      <c r="J4" s="4"/>
+      <c r="J4" s="4">
+        <v>2652</v>
+      </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -1263,7 +1284,9 @@
       <c r="Q4" s="4">
         <v>2784</v>
       </c>
-      <c r="R4" s="4"/>
+      <c r="R4" s="4">
+        <v>2652</v>
+      </c>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
@@ -1353,7 +1376,10 @@
         <f>1266+590+198</f>
         <v>2054</v>
       </c>
-      <c r="J5" s="4"/>
+      <c r="J5" s="4">
+        <f>1273+578+189</f>
+        <v>2040</v>
+      </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1371,7 +1397,10 @@
         <f>1264+590+206</f>
         <v>2060</v>
       </c>
-      <c r="R5" s="4"/>
+      <c r="R5" s="4">
+        <f>1273+578+189</f>
+        <v>2040</v>
+      </c>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
@@ -1460,7 +1489,9 @@
       <c r="I6" s="4">
         <v>241</v>
       </c>
-      <c r="J6" s="4"/>
+      <c r="J6" s="4">
+        <v>256</v>
+      </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1476,7 +1507,9 @@
       <c r="Q6" s="4">
         <v>226</v>
       </c>
-      <c r="R6" s="4"/>
+      <c r="R6" s="4">
+        <v>256</v>
+      </c>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
@@ -1565,7 +1598,9 @@
       <c r="I7" s="4">
         <v>199</v>
       </c>
-      <c r="J7" s="4"/>
+      <c r="J7" s="4">
+        <v>191</v>
+      </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -1581,7 +1616,9 @@
       <c r="Q7" s="4">
         <v>191</v>
       </c>
-      <c r="R7" s="4"/>
+      <c r="R7" s="4">
+        <v>191</v>
+      </c>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
@@ -1660,15 +1697,27 @@
       <c r="I8" s="4">
         <v>50</v>
       </c>
-      <c r="J8" s="4"/>
+      <c r="J8" s="4">
+        <v>52</v>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>47</v>
+      </c>
+      <c r="R8" s="4">
+        <v>52</v>
+      </c>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
@@ -1764,33 +1813,39 @@
         <f t="shared" si="0"/>
         <v>12453</v>
       </c>
-      <c r="J9" s="25"/>
+      <c r="J9" s="25">
+        <f t="shared" ref="J9" si="1">+SUM(J3:J7)</f>
+        <v>12342</v>
+      </c>
       <c r="K9" s="25"/>
       <c r="L9" s="25">
-        <f t="shared" ref="L9:Q9" si="1">+SUM(L3:L7)</f>
+        <f t="shared" ref="L9:R9" si="2">+SUM(L3:L7)</f>
         <v>0</v>
       </c>
       <c r="M9" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N9" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11794</v>
       </c>
       <c r="O9" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11939</v>
       </c>
       <c r="P9" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12154</v>
       </c>
       <c r="Q9" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12396</v>
       </c>
-      <c r="R9" s="4"/>
+      <c r="R9" s="25">
+        <f t="shared" si="2"/>
+        <v>12342</v>
+      </c>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
@@ -1962,7 +2017,10 @@
       <c r="I11" s="3">
         <v>16390</v>
       </c>
-      <c r="J11" s="3"/>
+      <c r="J11" s="3">
+        <f>+R11-I11</f>
+        <v>15059</v>
+      </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -1978,7 +2036,9 @@
       <c r="Q11" s="3">
         <v>29202</v>
       </c>
-      <c r="R11" s="3"/>
+      <c r="R11" s="3">
+        <v>31449</v>
+      </c>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
@@ -2050,27 +2110,30 @@
         <v>14036</v>
       </c>
       <c r="D12" s="3">
-        <f t="shared" ref="D12:D33" si="2">+O12-C12</f>
+        <f t="shared" ref="D12:D33" si="3">+O12-C12</f>
         <v>15487</v>
       </c>
       <c r="E12" s="4">
         <v>16313</v>
       </c>
       <c r="F12" s="4">
-        <f t="shared" ref="F12:F33" si="3">+P12-E12</f>
+        <f t="shared" ref="F12:F33" si="4">+P12-E12</f>
         <v>18754</v>
       </c>
       <c r="G12" s="4">
         <v>18082</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" ref="H12:H33" si="4">+Q12-G12</f>
+        <f t="shared" ref="H12:H33" si="5">+Q12-G12</f>
         <v>21303</v>
       </c>
       <c r="I12" s="4">
         <v>20886</v>
       </c>
-      <c r="J12" s="4"/>
+      <c r="J12" s="3">
+        <f>+R12-I12</f>
+        <v>24928</v>
+      </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -2086,7 +2149,9 @@
       <c r="Q12" s="4">
         <v>39385</v>
       </c>
-      <c r="R12" s="4"/>
+      <c r="R12" s="4">
+        <v>45814</v>
+      </c>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
@@ -2158,27 +2223,30 @@
         <v>818</v>
       </c>
       <c r="D13" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>839</v>
       </c>
       <c r="E13" s="4">
         <v>925</v>
       </c>
       <c r="F13" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1032</v>
       </c>
       <c r="G13" s="4">
         <v>1018</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1221</v>
       </c>
       <c r="I13" s="4">
         <v>1268</v>
       </c>
-      <c r="J13" s="4"/>
+      <c r="J13" s="3">
+        <f>+R13-I13</f>
+        <v>1638</v>
+      </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -2194,7 +2262,9 @@
       <c r="Q13" s="4">
         <v>2239</v>
       </c>
-      <c r="R13" s="4"/>
+      <c r="R13" s="4">
+        <v>2906</v>
+      </c>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
@@ -2266,27 +2336,30 @@
         <v>13360</v>
       </c>
       <c r="D14" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>14363</v>
       </c>
       <c r="E14" s="4">
         <v>14170</v>
       </c>
       <c r="F14" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16136</v>
       </c>
       <c r="G14" s="4">
         <v>16077</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>17445</v>
       </c>
       <c r="I14" s="4">
         <v>16950</v>
       </c>
-      <c r="J14" s="4"/>
+      <c r="J14" s="3">
+        <f>+R14-I14</f>
+        <v>17804</v>
+      </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -2302,7 +2375,9 @@
       <c r="Q14" s="4">
         <v>33522</v>
       </c>
-      <c r="R14" s="4"/>
+      <c r="R14" s="4">
+        <v>34754</v>
+      </c>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
@@ -2374,27 +2449,30 @@
         <v>10777</v>
       </c>
       <c r="D15" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10746</v>
       </c>
       <c r="E15" s="4">
         <v>12229</v>
       </c>
       <c r="F15" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12874</v>
       </c>
       <c r="G15" s="4">
         <v>13056</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13570</v>
       </c>
       <c r="I15" s="4">
         <v>14182</v>
       </c>
-      <c r="J15" s="4"/>
+      <c r="J15" s="3">
+        <f>+R15-I15</f>
+        <v>14287</v>
+      </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -2410,7 +2488,9 @@
       <c r="Q15" s="4">
         <v>26626</v>
       </c>
-      <c r="R15" s="4"/>
+      <c r="R15" s="4">
+        <v>28469</v>
+      </c>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
@@ -2482,27 +2562,30 @@
         <v>1828</v>
       </c>
       <c r="D16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2577</v>
       </c>
       <c r="E16" s="4">
         <v>3246</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3701</v>
       </c>
       <c r="G16" s="4">
         <v>4602</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6076</v>
       </c>
       <c r="I16" s="4">
         <v>7412</v>
       </c>
-      <c r="J16" s="4"/>
+      <c r="J16" s="3">
+        <f>+R16-I16</f>
+        <v>9584</v>
+      </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -2518,7 +2601,9 @@
       <c r="Q16" s="4">
         <v>10678</v>
       </c>
-      <c r="R16" s="4"/>
+      <c r="R16" s="4">
+        <v>16996</v>
+      </c>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
@@ -2590,27 +2675,30 @@
         <v>6640</v>
       </c>
       <c r="D17" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7047</v>
       </c>
       <c r="E17" s="4">
         <v>8085</v>
       </c>
       <c r="F17" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8920</v>
       </c>
       <c r="G17" s="4">
         <v>8937</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9301</v>
       </c>
       <c r="I17" s="4">
         <v>9413</v>
       </c>
-      <c r="J17" s="4"/>
+      <c r="J17" s="3">
+        <f>+R17-I17</f>
+        <v>9292</v>
+      </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -2626,7 +2714,10 @@
       <c r="Q17" s="4">
         <v>18238</v>
       </c>
-      <c r="R17" s="4"/>
+      <c r="R17" s="4">
+        <f>12310+6395</f>
+        <v>18705</v>
+      </c>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
       <c r="U17" s="4"/>
@@ -2698,27 +2789,30 @@
         <v>4569</v>
       </c>
       <c r="D18" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4108</v>
       </c>
       <c r="E18" s="4">
         <v>4635</v>
       </c>
       <c r="F18" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5296</v>
       </c>
       <c r="G18" s="4">
         <v>5567</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6418</v>
       </c>
       <c r="I18" s="4">
         <v>6131</v>
       </c>
-      <c r="J18" s="4"/>
+      <c r="J18" s="3">
+        <f>+R18-I18</f>
+        <v>6732</v>
+      </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -2734,7 +2828,9 @@
       <c r="Q18" s="4">
         <v>11985</v>
       </c>
-      <c r="R18" s="4"/>
+      <c r="R18" s="4">
+        <v>12863</v>
+      </c>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
       <c r="U18" s="4"/>
@@ -2806,27 +2902,30 @@
         <v>2151</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2208</v>
       </c>
       <c r="E19" s="4">
         <v>1450</v>
       </c>
       <c r="F19" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1920</v>
       </c>
       <c r="G19" s="4">
         <v>1573</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1726</v>
       </c>
       <c r="I19" s="4">
         <v>1406</v>
       </c>
-      <c r="J19" s="4"/>
+      <c r="J19" s="3">
+        <f>+R19-I19</f>
+        <v>1780</v>
+      </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -2842,7 +2941,9 @@
       <c r="Q19" s="4">
         <v>3299</v>
       </c>
-      <c r="R19" s="4"/>
+      <c r="R19" s="4">
+        <v>3186</v>
+      </c>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
       <c r="U19" s="4"/>
@@ -2921,20 +3022,23 @@
         <v>29645</v>
       </c>
       <c r="F20" s="25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>32711</v>
       </c>
       <c r="G20" s="25">
         <v>33735</v>
       </c>
       <c r="H20" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>37091</v>
       </c>
       <c r="I20" s="25">
         <v>38544</v>
       </c>
-      <c r="J20" s="25"/>
+      <c r="J20" s="24">
+        <f>+R20-I20</f>
+        <v>41675</v>
+      </c>
       <c r="K20" s="25"/>
       <c r="L20" s="25"/>
       <c r="M20" s="25">
@@ -2952,7 +3056,9 @@
       <c r="Q20" s="25">
         <v>70826</v>
       </c>
-      <c r="R20" s="25"/>
+      <c r="R20" s="25">
+        <v>80219</v>
+      </c>
       <c r="S20" s="25"/>
       <c r="T20" s="25"/>
       <c r="U20" s="25"/>
@@ -3024,27 +3130,30 @@
         <v>9856</v>
       </c>
       <c r="D21" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>11477</v>
       </c>
       <c r="E21" s="4">
         <v>10890</v>
       </c>
       <c r="F21" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12438</v>
       </c>
       <c r="G21" s="4">
         <v>12117</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14677</v>
       </c>
       <c r="I21" s="4">
         <v>14119</v>
       </c>
-      <c r="J21" s="4"/>
+      <c r="J21" s="3">
+        <f>+R21-I21</f>
+        <v>16366</v>
+      </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -3060,7 +3169,9 @@
       <c r="Q21" s="4">
         <v>26794</v>
       </c>
-      <c r="R21" s="4"/>
+      <c r="R21" s="4">
+        <v>30485</v>
+      </c>
       <c r="S21" s="4"/>
       <c r="T21" s="4"/>
       <c r="U21" s="4"/>
@@ -3129,11 +3240,11 @@
         <v>44</v>
       </c>
       <c r="C22" s="4">
-        <f t="shared" ref="C22:D22" si="5">+C20-C21</f>
+        <f t="shared" ref="C22:D22" si="6">+C20-C21</f>
         <v>16109</v>
       </c>
       <c r="D22" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>16209</v>
       </c>
       <c r="E22" s="4">
@@ -3141,48 +3252,54 @@
         <v>18755</v>
       </c>
       <c r="F22" s="4">
-        <f t="shared" ref="F22:I22" si="6">+F20-F21</f>
+        <f t="shared" ref="F22:J22" si="7">+F20-F21</f>
         <v>20273</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>21618</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>22414</v>
       </c>
       <c r="I22" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>24425</v>
       </c>
-      <c r="J22" s="4"/>
+      <c r="J22" s="4">
+        <f t="shared" si="7"/>
+        <v>25309</v>
+      </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4">
-        <f t="shared" ref="L22:P22" si="7">+L20-L21</f>
+        <f t="shared" ref="L22:P22" si="8">+L20-L21</f>
         <v>0</v>
       </c>
       <c r="M22" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>35512</v>
       </c>
       <c r="N22" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>30404</v>
       </c>
       <c r="O22" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>32318</v>
       </c>
       <c r="P22" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>39028</v>
       </c>
       <c r="Q22" s="4">
         <f>+Q20-Q21</f>
         <v>44032</v>
       </c>
-      <c r="R22" s="4"/>
+      <c r="R22" s="4">
+        <f>+R20-R21</f>
+        <v>49734</v>
+      </c>
       <c r="S22" s="4"/>
       <c r="T22" s="4"/>
       <c r="U22" s="4"/>
@@ -3254,27 +3371,30 @@
         <v>821</v>
       </c>
       <c r="D23" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1307</v>
       </c>
       <c r="E23" s="4">
         <v>637</v>
       </c>
       <c r="F23" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1068</v>
       </c>
       <c r="G23" s="4">
         <v>809</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1599</v>
       </c>
       <c r="I23" s="4">
         <v>1315</v>
       </c>
-      <c r="J23" s="4"/>
+      <c r="J23" s="3">
+        <f>+R23-I23</f>
+        <v>1684</v>
+      </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -3290,7 +3410,9 @@
       <c r="Q23" s="4">
         <v>2408</v>
       </c>
-      <c r="R23" s="4"/>
+      <c r="R23" s="4">
+        <v>2999</v>
+      </c>
       <c r="S23" s="4"/>
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
@@ -3362,27 +3484,30 @@
         <v>9437</v>
       </c>
       <c r="D24" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10192</v>
       </c>
       <c r="E24" s="4">
         <v>10074</v>
       </c>
       <c r="F24" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>11599</v>
       </c>
       <c r="G24" s="4">
         <v>11796</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13851</v>
       </c>
       <c r="I24" s="4">
         <v>13272</v>
       </c>
-      <c r="J24" s="4"/>
+      <c r="J24" s="3">
+        <f>+R24-I24</f>
+        <v>15184</v>
+      </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -3398,7 +3523,9 @@
       <c r="Q24" s="4">
         <v>25647</v>
       </c>
-      <c r="R24" s="4"/>
+      <c r="R24" s="4">
+        <v>28456</v>
+      </c>
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
       <c r="U24" s="4"/>
@@ -3470,27 +3597,30 @@
         <v>1701</v>
       </c>
       <c r="D25" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1886</v>
       </c>
       <c r="E25" s="4">
         <v>1695</v>
       </c>
       <c r="F25" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1998</v>
       </c>
       <c r="G25" s="4">
         <v>1971</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2227</v>
       </c>
       <c r="I25" s="4">
         <v>2337</v>
       </c>
-      <c r="J25" s="4"/>
+      <c r="J25" s="3">
+        <f>+R25-I25</f>
+        <v>2849</v>
+      </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -3506,7 +3636,9 @@
       <c r="Q25" s="4">
         <v>4198</v>
       </c>
-      <c r="R25" s="4"/>
+      <c r="R25" s="4">
+        <v>5186</v>
+      </c>
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
       <c r="U25" s="4"/>
@@ -3575,19 +3707,19 @@
         <v>48</v>
       </c>
       <c r="C26" s="4">
-        <f t="shared" ref="C26:F26" si="8">+C22+C23-SUM(C24:C25)</f>
+        <f t="shared" ref="C26:F26" si="9">+C22+C23-SUM(C24:C25)</f>
         <v>5792</v>
       </c>
       <c r="D26" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5438</v>
       </c>
       <c r="E26" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7623</v>
       </c>
       <c r="F26" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7744</v>
       </c>
       <c r="G26" s="4">
@@ -3595,40 +3727,46 @@
         <v>8660</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" ref="H26:Q26" si="9">+H22+H23-SUM(H24:H25)</f>
+        <f t="shared" ref="H26:R26" si="10">+H22+H23-SUM(H24:H25)</f>
         <v>7935</v>
       </c>
       <c r="I26" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10131</v>
       </c>
-      <c r="J26" s="4"/>
+      <c r="J26" s="4">
+        <f t="shared" si="10"/>
+        <v>8960</v>
+      </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M26" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>35512</v>
       </c>
       <c r="N26" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10989</v>
       </c>
       <c r="O26" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11230</v>
       </c>
       <c r="P26" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>15367</v>
       </c>
       <c r="Q26" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>16595</v>
       </c>
-      <c r="R26" s="4"/>
+      <c r="R26" s="4">
+        <f t="shared" si="10"/>
+        <v>19091</v>
+      </c>
       <c r="S26" s="4"/>
       <c r="T26" s="4"/>
       <c r="U26" s="4"/>
@@ -3700,27 +3838,30 @@
         <v>-22</v>
       </c>
       <c r="D27" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>119</v>
       </c>
       <c r="E27" s="4">
         <v>356</v>
       </c>
       <c r="F27" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>635</v>
       </c>
       <c r="G27" s="4">
         <v>710</v>
       </c>
       <c r="H27" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>678</v>
       </c>
       <c r="I27" s="4">
         <v>596</v>
       </c>
-      <c r="J27" s="4"/>
+      <c r="J27" s="3">
+        <f>+R27-I27</f>
+        <v>555</v>
+      </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -3736,7 +3877,9 @@
       <c r="Q27" s="4">
         <v>1388</v>
       </c>
-      <c r="R27" s="4"/>
+      <c r="R27" s="4">
+        <v>1151</v>
+      </c>
       <c r="S27" s="4"/>
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
@@ -3808,27 +3951,30 @@
         <v>-178</v>
       </c>
       <c r="D28" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>206</v>
       </c>
       <c r="E28" s="4">
         <v>-516</v>
       </c>
       <c r="F28" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-202</v>
       </c>
       <c r="G28" s="4">
         <v>-19</v>
       </c>
       <c r="H28" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>217</v>
       </c>
       <c r="I28" s="4">
         <v>434</v>
       </c>
-      <c r="J28" s="4"/>
+      <c r="J28" s="3">
+        <f>+R28-I28</f>
+        <v>769</v>
+      </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -3844,7 +3990,9 @@
       <c r="Q28" s="4">
         <v>198</v>
       </c>
-      <c r="R28" s="4"/>
+      <c r="R28" s="4">
+        <v>1203</v>
+      </c>
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
@@ -3916,27 +4064,30 @@
         <v>0</v>
       </c>
       <c r="D29" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
       </c>
       <c r="F29" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G29" s="4">
         <v>1579</v>
       </c>
       <c r="H29" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2124</v>
       </c>
       <c r="I29" s="4">
         <v>0</v>
       </c>
-      <c r="J29" s="4"/>
+      <c r="J29" s="3">
+        <f>+R29-I29</f>
+        <v>1</v>
+      </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -3953,7 +4104,9 @@
         <f>1579+2090+34</f>
         <v>3703</v>
       </c>
-      <c r="R29" s="4"/>
+      <c r="R29" s="4">
+        <v>1</v>
+      </c>
       <c r="S29" s="4"/>
       <c r="T29" s="4"/>
       <c r="U29" s="4"/>
@@ -4022,19 +4175,19 @@
         <v>52</v>
       </c>
       <c r="C30" s="4">
-        <f t="shared" ref="C30:F30" si="10">+C26+SUM(C27:C29)</f>
+        <f t="shared" ref="C30:F30" si="11">+C26+SUM(C27:C29)</f>
         <v>5592</v>
       </c>
       <c r="D30" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5763</v>
       </c>
       <c r="E30" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7463</v>
       </c>
       <c r="F30" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8177</v>
       </c>
       <c r="G30" s="4">
@@ -4042,40 +4195,46 @@
         <v>10930</v>
       </c>
       <c r="H30" s="4">
-        <f t="shared" ref="H30:Q30" si="11">+H26+SUM(H27:H29)</f>
+        <f t="shared" ref="H30:R30" si="12">+H26+SUM(H27:H29)</f>
         <v>10954</v>
       </c>
       <c r="I30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11161</v>
       </c>
-      <c r="J30" s="4"/>
+      <c r="J30" s="4">
+        <f t="shared" si="12"/>
+        <v>10285</v>
+      </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>35512</v>
       </c>
       <c r="N30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11240</v>
       </c>
       <c r="O30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11355</v>
       </c>
       <c r="P30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15640</v>
       </c>
       <c r="Q30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>21884</v>
       </c>
-      <c r="R30" s="4"/>
+      <c r="R30" s="4">
+        <f t="shared" si="12"/>
+        <v>21446</v>
+      </c>
       <c r="S30" s="4"/>
       <c r="T30" s="4"/>
       <c r="U30" s="4"/>
@@ -4147,27 +4306,30 @@
         <v>1642</v>
       </c>
       <c r="D31" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1468</v>
       </c>
       <c r="E31" s="4">
         <v>2169</v>
       </c>
       <c r="F31" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2194</v>
       </c>
       <c r="G31" s="4">
         <v>2511</v>
       </c>
       <c r="H31" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2384</v>
       </c>
       <c r="I31" s="4">
         <v>3050</v>
       </c>
-      <c r="J31" s="4"/>
+      <c r="J31" s="3">
+        <f>+R31-I31</f>
+        <v>2734</v>
+      </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -4183,7 +4345,9 @@
       <c r="Q31" s="4">
         <v>4895</v>
       </c>
-      <c r="R31" s="4"/>
+      <c r="R31" s="4">
+        <v>5784</v>
+      </c>
       <c r="S31" s="4"/>
       <c r="T31" s="4"/>
       <c r="U31" s="4"/>
@@ -4252,19 +4416,19 @@
         <v>54</v>
       </c>
       <c r="C32" s="4">
-        <f t="shared" ref="C32:F32" si="12">+C30-C31</f>
+        <f t="shared" ref="C32:F32" si="13">+C30-C31</f>
         <v>3950</v>
       </c>
       <c r="D32" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4295</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5294</v>
       </c>
       <c r="F32" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5983</v>
       </c>
       <c r="G32" s="4">
@@ -4272,40 +4436,46 @@
         <v>8419</v>
       </c>
       <c r="H32" s="4">
-        <f t="shared" ref="H32:I32" si="13">+H30-H31</f>
+        <f t="shared" ref="H32:J32" si="14">+H30-H31</f>
         <v>8570</v>
       </c>
       <c r="I32" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8111</v>
       </c>
-      <c r="J32" s="4"/>
+      <c r="J32" s="4">
+        <f t="shared" si="14"/>
+        <v>7551</v>
+      </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4">
-        <f t="shared" ref="L32:P32" si="14">+L30-L31</f>
+        <f t="shared" ref="L32:P32" si="15">+L30-L31</f>
         <v>0</v>
       </c>
       <c r="M32" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>35512</v>
       </c>
       <c r="N32" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8219</v>
       </c>
       <c r="O32" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8245</v>
       </c>
       <c r="P32" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>11277</v>
       </c>
       <c r="Q32" s="4">
         <f>+Q30-Q31</f>
         <v>16989</v>
       </c>
-      <c r="R32" s="4"/>
+      <c r="R32" s="4">
+        <f>+R30-R31</f>
+        <v>15662</v>
+      </c>
       <c r="S32" s="4"/>
       <c r="T32" s="4"/>
       <c r="U32" s="4"/>
@@ -4377,27 +4547,30 @@
         <v>362</v>
       </c>
       <c r="D33" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>293</v>
       </c>
       <c r="E33" s="4">
         <v>546</v>
       </c>
       <c r="F33" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>495</v>
       </c>
       <c r="G33" s="4">
         <v>698</v>
       </c>
       <c r="H33" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>695</v>
       </c>
       <c r="I33" s="4">
         <v>1080</v>
       </c>
-      <c r="J33" s="4"/>
+      <c r="J33" s="3">
+        <f>+R33-I33</f>
+        <v>994</v>
+      </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -4413,7 +4586,9 @@
       <c r="Q33" s="4">
         <v>1393</v>
       </c>
-      <c r="R33" s="4"/>
+      <c r="R33" s="4">
+        <v>2074</v>
+      </c>
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
       <c r="U33" s="4"/>
@@ -4482,19 +4657,19 @@
         <v>56</v>
       </c>
       <c r="C34" s="4">
-        <f t="shared" ref="C34:F34" si="15">+C32-C33</f>
+        <f t="shared" ref="C34:F34" si="16">+C32-C33</f>
         <v>3588</v>
       </c>
       <c r="D34" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4002</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4748</v>
       </c>
       <c r="F34" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5488</v>
       </c>
       <c r="G34" s="4">
@@ -4502,40 +4677,46 @@
         <v>7721</v>
       </c>
       <c r="H34" s="4">
-        <f t="shared" ref="H34:I34" si="16">+H32-H33</f>
+        <f t="shared" ref="H34:J34" si="17">+H32-H33</f>
         <v>7875</v>
       </c>
       <c r="I34" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>7031</v>
       </c>
-      <c r="J34" s="4"/>
+      <c r="J34" s="4">
+        <f t="shared" si="17"/>
+        <v>6557</v>
+      </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4">
-        <f t="shared" ref="L34:P34" si="17">+L32-L33</f>
+        <f t="shared" ref="L34:P34" si="18">+L32-L33</f>
         <v>0</v>
       </c>
       <c r="M34" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>35512</v>
       </c>
       <c r="N34" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>7720</v>
       </c>
       <c r="O34" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>7590</v>
       </c>
       <c r="P34" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>10236</v>
       </c>
       <c r="Q34" s="4">
         <f>+Q32-Q33</f>
         <v>15596</v>
       </c>
-      <c r="R34" s="4"/>
+      <c r="R34" s="4">
+        <f>+R32-R33</f>
+        <v>13588</v>
+      </c>
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
@@ -4684,11 +4865,11 @@
         <v>57</v>
       </c>
       <c r="C36" s="26">
-        <f t="shared" ref="C36:D36" si="18">+C34/C37</f>
+        <f t="shared" ref="C36:D36" si="19">+C34/C37</f>
         <v>1.3330291787752626</v>
       </c>
       <c r="D36" s="26">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.4864901004662274</v>
       </c>
       <c r="E36" s="26">
@@ -4696,48 +4877,54 @@
         <v>1.7353820197902265</v>
       </c>
       <c r="F36" s="26">
-        <f t="shared" ref="F36:I36" si="19">+F34/F37</f>
+        <f t="shared" ref="F36:J36" si="20">+F34/F37</f>
         <v>1.9778394050624473</v>
       </c>
       <c r="G36" s="26">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.7461456684273626</v>
       </c>
       <c r="H36" s="26">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.8041107016614935</v>
       </c>
       <c r="I36" s="26">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.5281563480060609</v>
       </c>
-      <c r="J36" s="26"/>
+      <c r="J36" s="26">
+        <f t="shared" si="20"/>
+        <v>2.3582666290705907</v>
+      </c>
       <c r="K36" s="4"/>
       <c r="L36" s="26" t="e">
-        <f t="shared" ref="L36:P36" si="20">+L34/L37</f>
+        <f t="shared" ref="L36:P36" si="21">+L34/L37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M36" s="26" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N36" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.8695321844796968</v>
       </c>
       <c r="O36" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.8192053629531899</v>
       </c>
       <c r="P36" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3.6889876367017513</v>
       </c>
       <c r="Q36" s="26">
         <f>+Q34/Q37</f>
         <v>5.5533854607127182</v>
       </c>
-      <c r="R36" s="4"/>
+      <c r="R36" s="26">
+        <f>+R34/R37</f>
+        <v>4.8870103638571276</v>
+      </c>
       <c r="S36" s="4"/>
       <c r="T36" s="4"/>
       <c r="U36" s="4"/>
@@ -4829,7 +5016,9 @@
       <c r="I37" s="4">
         <v>2781.078</v>
       </c>
-      <c r="J37" s="4"/>
+      <c r="J37" s="4">
+        <v>2780.4319999999998</v>
+      </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
@@ -4845,7 +5034,9 @@
       <c r="Q37" s="4">
         <v>2808.377</v>
       </c>
-      <c r="R37" s="4"/>
+      <c r="R37" s="4">
+        <v>2780.4319999999998</v>
+      </c>
       <c r="S37" s="4"/>
       <c r="T37" s="4"/>
       <c r="U37" s="4"/>
@@ -5015,7 +5206,10 @@
         <f>+I9/G9-1</f>
         <v>1.7235745793171109E-2</v>
       </c>
-      <c r="J39" s="27"/>
+      <c r="J39" s="27">
+        <f>+J9/H9-1</f>
+        <v>-8.1170135819336187E-3</v>
+      </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="27" t="e">
@@ -5038,7 +5232,10 @@
         <f>+Q9/P9-1</f>
         <v>1.991114036531183E-2</v>
       </c>
-      <c r="R39" s="4"/>
+      <c r="R39" s="27">
+        <f>+R9/Q9-1</f>
+        <v>-4.3562439496611649E-3</v>
+      </c>
       <c r="S39" s="4"/>
       <c r="T39" s="4"/>
       <c r="U39" s="4"/>
@@ -5109,11 +5306,11 @@
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="27">
-        <f t="shared" ref="E40:F49" si="21">+E11/C11-1</f>
+        <f t="shared" ref="E40:F49" si="22">+E11/C11-1</f>
         <v>0.11664116641166422</v>
       </c>
       <c r="F40" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.13776408450704225</v>
       </c>
       <c r="G40" s="27">
@@ -5121,37 +5318,43 @@
         <v>0.17957604578060771</v>
       </c>
       <c r="H40" s="27">
-        <f t="shared" ref="H40:I49" si="22">+H11/F11-1</f>
+        <f t="shared" ref="H40:J49" si="23">+H11/F11-1</f>
         <v>0.12704061895551266</v>
       </c>
       <c r="I40" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.11991800478305437</v>
       </c>
-      <c r="J40" s="27"/>
+      <c r="J40" s="27">
+        <f t="shared" si="23"/>
+        <v>3.3774970824466344E-2</v>
+      </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="27" t="e">
-        <f t="shared" ref="M40:P49" si="23">+M11/L11-1</f>
+        <f t="shared" ref="M40:P49" si="24">+M11/L11-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N40" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O40" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.17409478029155134</v>
       </c>
       <c r="P40" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.12731965644608612</v>
       </c>
       <c r="Q40" s="27">
         <f>+Q11/P11-1</f>
         <v>0.15277119848413068</v>
       </c>
-      <c r="R40" s="4"/>
+      <c r="R40" s="27">
+        <f>+R11/Q11-1</f>
+        <v>7.6946784466817242E-2</v>
+      </c>
       <c r="S40" s="4"/>
       <c r="T40" s="4"/>
       <c r="U40" s="4"/>
@@ -5222,49 +5425,55 @@
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.16222570532915359</v>
       </c>
       <c r="F41" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.21095112029444052</v>
       </c>
       <c r="G41" s="27">
-        <f t="shared" ref="G41:G49" si="24">+G12/E12-1</f>
+        <f t="shared" ref="G41:G49" si="25">+G12/E12-1</f>
         <v>0.1084411205786795</v>
       </c>
       <c r="H41" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.13591767089687523</v>
       </c>
       <c r="I41" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.15507134166574499</v>
       </c>
-      <c r="J41" s="27"/>
+      <c r="J41" s="27">
+        <f t="shared" si="23"/>
+        <v>0.17016382669107633</v>
+      </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
       <c r="M41" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N41" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O41" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>3.111902766135799E-2</v>
       </c>
       <c r="P41" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.18778579412661323</v>
       </c>
       <c r="Q41" s="27">
-        <f t="shared" ref="Q41:Q49" si="25">+Q12/P12-1</f>
+        <f t="shared" ref="Q41:R49" si="26">+Q12/P12-1</f>
         <v>0.12313571163772208</v>
       </c>
-      <c r="R41" s="4"/>
+      <c r="R41" s="27">
+        <f t="shared" si="26"/>
+        <v>0.16323473403580047</v>
+      </c>
       <c r="S41" s="4"/>
       <c r="T41" s="4"/>
       <c r="U41" s="4"/>
@@ -5335,49 +5544,55 @@
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.13080684596577008</v>
       </c>
       <c r="F42" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.23003575685339683</v>
       </c>
       <c r="G42" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.10054054054054062</v>
       </c>
       <c r="H42" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.18313953488372103</v>
       </c>
       <c r="I42" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.24557956777996082</v>
       </c>
-      <c r="J42" s="27"/>
+      <c r="J42" s="27">
+        <f t="shared" si="23"/>
+        <v>0.34152334152334163</v>
+      </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N42" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O42" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6.4226075786769421E-2</v>
       </c>
       <c r="P42" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.18105009052504517</v>
       </c>
       <c r="Q42" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.14409810935104761</v>
       </c>
-      <c r="R42" s="4"/>
+      <c r="R42" s="27">
+        <f t="shared" si="26"/>
+        <v>0.29790084859312183</v>
+      </c>
       <c r="S42" s="4"/>
       <c r="T42" s="4"/>
       <c r="U42" s="4"/>
@@ -5448,49 +5663,55 @@
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>6.062874251497008E-2</v>
       </c>
       <c r="F43" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.12344217781800459</v>
       </c>
       <c r="G43" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.13458009880028232</v>
       </c>
       <c r="H43" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>8.1122954883490417E-2</v>
       </c>
       <c r="I43" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5.4301175592461171E-2</v>
       </c>
-      <c r="J43" s="27"/>
+      <c r="J43" s="27">
+        <f t="shared" si="23"/>
+        <v>2.0578962453424943E-2</v>
+      </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N43" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O43" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.15454772613693146</v>
       </c>
       <c r="P43" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.3171734660751016E-2</v>
       </c>
       <c r="Q43" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.1061176004751534</v>
       </c>
-      <c r="R43" s="4"/>
+      <c r="R43" s="27">
+        <f t="shared" si="26"/>
+        <v>3.6751983771851293E-2</v>
+      </c>
       <c r="S43" s="4"/>
       <c r="T43" s="4"/>
       <c r="U43" s="4"/>
@@ -5561,49 +5782,55 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.134731372367078</v>
       </c>
       <c r="F44" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.19802717290154481</v>
       </c>
       <c r="G44" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6.7626134598086418E-2</v>
       </c>
       <c r="H44" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5.4062451452540072E-2</v>
       </c>
       <c r="I44" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>8.6243872549019551E-2</v>
       </c>
-      <c r="J44" s="27"/>
+      <c r="J44" s="27">
+        <f t="shared" si="23"/>
+        <v>5.2837140751658129E-2</v>
+      </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N44" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O44" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-1.3701768857116714E-2</v>
       </c>
       <c r="P44" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.16633368954142091</v>
       </c>
       <c r="Q44" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>6.0670039437517476E-2</v>
       </c>
-      <c r="R44" s="4"/>
+      <c r="R44" s="27">
+        <f t="shared" si="26"/>
+        <v>6.9218057537745015E-2</v>
+      </c>
       <c r="S44" s="4"/>
       <c r="T44" s="4"/>
       <c r="U44" s="4"/>
@@ -5674,49 +5901,55 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.775711159737418</v>
       </c>
       <c r="F45" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.43616608459448969</v>
       </c>
       <c r="G45" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.41774491682070236</v>
       </c>
       <c r="H45" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.64171845447176445</v>
       </c>
       <c r="I45" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.61060408518035647</v>
       </c>
-      <c r="J45" s="27"/>
+      <c r="J45" s="27">
+        <f t="shared" si="23"/>
+        <v>0.57735352205398294</v>
+      </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N45" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O45" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.26073268460217514</v>
       </c>
       <c r="P45" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.57707150964812715</v>
       </c>
       <c r="Q45" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.53706635957967475</v>
       </c>
-      <c r="R45" s="4"/>
+      <c r="R45" s="27">
+        <f t="shared" si="26"/>
+        <v>0.59168383592433038</v>
+      </c>
       <c r="S45" s="4"/>
       <c r="T45" s="4"/>
       <c r="U45" s="4"/>
@@ -5787,49 +6020,55 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.21762048192771077</v>
       </c>
       <c r="F46" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.26578685965659155</v>
       </c>
       <c r="G46" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.10538033395176249</v>
       </c>
       <c r="H46" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4.2713004484304928E-2</v>
       </c>
       <c r="I46" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5.3261720935436907E-2</v>
       </c>
-      <c r="J46" s="27"/>
+      <c r="J46" s="27">
+        <f t="shared" si="23"/>
+        <v>-9.6763788839904219E-4</v>
+      </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N46" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O46" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.60007014262333414</v>
       </c>
       <c r="P46" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.24241981442244476</v>
       </c>
       <c r="Q46" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7.2508085857100779E-2</v>
       </c>
-      <c r="R46" s="4"/>
+      <c r="R46" s="27">
+        <f t="shared" si="26"/>
+        <v>2.5605877837482138E-2</v>
+      </c>
       <c r="S46" s="4"/>
       <c r="T46" s="4"/>
       <c r="U46" s="4"/>
@@ -5900,49 +6139,55 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1.4445173998686833E-2</v>
       </c>
       <c r="F47" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.28919182083739048</v>
       </c>
       <c r="G47" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.20107874865156417</v>
       </c>
       <c r="H47" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.2118580060422961</v>
       </c>
       <c r="I47" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.10131129872462719</v>
       </c>
-      <c r="J47" s="27"/>
+      <c r="J47" s="27">
+        <f t="shared" si="23"/>
+        <v>4.8924898722343402E-2</v>
+      </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N47" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O47" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5.5467704658800576E-2</v>
       </c>
       <c r="P47" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.14451999539011173</v>
       </c>
       <c r="Q47" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.2068271070385661</v>
       </c>
-      <c r="R47" s="4"/>
+      <c r="R47" s="27">
+        <f t="shared" si="26"/>
+        <v>7.3258239465999075E-2</v>
+      </c>
       <c r="S47" s="4"/>
       <c r="T47" s="4"/>
       <c r="U47" s="4"/>
@@ -6013,49 +6258,55 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-0.32589493258949331</v>
       </c>
       <c r="F48" s="27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-0.13043478260869568</v>
       </c>
       <c r="G48" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>8.4827586206896566E-2</v>
       </c>
       <c r="H48" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-0.1010416666666667</v>
       </c>
       <c r="I48" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-0.10616656071201525</v>
       </c>
-      <c r="J48" s="27"/>
+      <c r="J48" s="27">
+        <f t="shared" si="23"/>
+        <v>3.1286210892236488E-2</v>
+      </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N48" s="27" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O48" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-0.39767859610335776</v>
       </c>
       <c r="P48" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-0.22688690066529016</v>
       </c>
       <c r="Q48" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-2.1068249258160199E-2</v>
       </c>
-      <c r="R48" s="4"/>
+      <c r="R48" s="27">
+        <f t="shared" si="26"/>
+        <v>-3.4252803879963656E-2</v>
+      </c>
       <c r="S48" s="4"/>
       <c r="T48" s="4"/>
       <c r="U48" s="4"/>
@@ -6126,49 +6377,55 @@
       <c r="C49" s="24"/>
       <c r="D49" s="24"/>
       <c r="E49" s="28">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.14172925091469279</v>
       </c>
       <c r="F49" s="28">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.18149967492595542</v>
       </c>
       <c r="G49" s="28">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.13796593017372238</v>
       </c>
       <c r="H49" s="28">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.13389991134480761</v>
       </c>
       <c r="I49" s="28">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.14255224544241885</v>
       </c>
-      <c r="J49" s="28"/>
+      <c r="J49" s="28">
+        <f t="shared" si="23"/>
+        <v>0.12358793238251864</v>
+      </c>
       <c r="K49" s="25"/>
       <c r="L49" s="25"/>
       <c r="M49" s="28" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N49" s="28">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.38905158819553964</v>
       </c>
       <c r="O49" s="28">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8.7637852740836797E-2</v>
       </c>
       <c r="P49" s="28">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.16225233453244114</v>
       </c>
       <c r="Q49" s="28">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.13583295913785354</v>
       </c>
-      <c r="R49" s="25"/>
+      <c r="R49" s="28">
+        <f t="shared" si="26"/>
+        <v>0.13262078897579976</v>
+      </c>
       <c r="S49" s="25"/>
       <c r="T49" s="25"/>
       <c r="U49" s="25"/>
@@ -6237,19 +6494,19 @@
         <v>69</v>
       </c>
       <c r="C50" s="27">
-        <f t="shared" ref="C50:F50" si="26">+C22/C20</f>
+        <f t="shared" ref="C50:F50" si="27">+C22/C20</f>
         <v>0.62041209320238788</v>
       </c>
       <c r="D50" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.58545835440294736</v>
       </c>
       <c r="E50" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.63265306122448983</v>
       </c>
       <c r="F50" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.61976093668796428</v>
       </c>
       <c r="G50" s="27">
@@ -6257,37 +6514,43 @@
         <v>0.6408181413961761</v>
       </c>
       <c r="H50" s="27">
-        <f t="shared" ref="H50:I50" si="27">+H22/H20</f>
+        <f t="shared" ref="H50:I50" si="28">+H22/H20</f>
         <v>0.60429753848642531</v>
       </c>
       <c r="I50" s="27">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.63369136571191365</v>
       </c>
-      <c r="J50" s="27"/>
+      <c r="J50" s="27">
+        <f t="shared" ref="J50" si="29">+J22/J20</f>
+        <v>0.6072945410917816</v>
+      </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="27">
-        <f t="shared" ref="M50:P50" si="28">+M22/M20</f>
+        <f t="shared" ref="M50:P50" si="30">+M22/M20</f>
         <v>1</v>
       </c>
       <c r="N50" s="27">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.61636393123580924</v>
       </c>
       <c r="O50" s="27">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.6023746062515144</v>
       </c>
       <c r="P50" s="27">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.62589005067675929</v>
       </c>
       <c r="Q50" s="27">
-        <f t="shared" ref="Q50" si="29">+Q22/Q20</f>
+        <f t="shared" ref="Q50:R50" si="31">+Q22/Q20</f>
         <v>0.62169259876316607</v>
       </c>
-      <c r="R50" s="4"/>
+      <c r="R50" s="27">
+        <f t="shared" si="31"/>
+        <v>0.61997781074309077</v>
+      </c>
       <c r="S50" s="4"/>
       <c r="T50" s="4"/>
       <c r="U50" s="4"/>
@@ -6356,19 +6619,19 @@
         <v>70</v>
       </c>
       <c r="C51" s="27">
-        <f t="shared" ref="C51:F51" si="30">+C26/C20</f>
+        <f t="shared" ref="C51:F51" si="32">+C26/C20</f>
         <v>0.22306951665703831</v>
       </c>
       <c r="D51" s="27">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.19641696164126274</v>
       </c>
       <c r="E51" s="27">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.25714285714285712</v>
       </c>
       <c r="F51" s="27">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.23673993457858214</v>
       </c>
       <c r="G51" s="27">
@@ -6376,37 +6639,43 @@
         <v>0.25670668445234918</v>
       </c>
       <c r="H51" s="27">
-        <f t="shared" ref="H51:I51" si="31">+H26/H20</f>
+        <f t="shared" ref="H51:I51" si="33">+H26/H20</f>
         <v>0.21393329918309023</v>
       </c>
       <c r="I51" s="27">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.26284246575342468</v>
       </c>
-      <c r="J51" s="27"/>
+      <c r="J51" s="27">
+        <f t="shared" ref="J51" si="34">+J26/J20</f>
+        <v>0.21499700059988003</v>
+      </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="27">
-        <f t="shared" ref="M51:P51" si="32">+M26/M20</f>
+        <f t="shared" ref="M51:P51" si="35">+M26/M20</f>
         <v>1</v>
       </c>
       <c r="N51" s="27">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0.22277408368472268</v>
       </c>
       <c r="O51" s="27">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0.2093157629867104</v>
       </c>
       <c r="P51" s="27">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0.24643979729296298</v>
       </c>
       <c r="Q51" s="27">
-        <f t="shared" ref="Q51" si="33">+Q26/Q20</f>
+        <f t="shared" ref="Q51:R51" si="36">+Q26/Q20</f>
         <v>0.23430661056674101</v>
       </c>
-      <c r="R51" s="4"/>
+      <c r="R51" s="27">
+        <f t="shared" si="36"/>
+        <v>0.2379860132886224</v>
+      </c>
       <c r="S51" s="4"/>
       <c r="T51" s="4"/>
       <c r="U51" s="4"/>
@@ -6475,19 +6744,19 @@
         <v>71</v>
       </c>
       <c r="C52" s="27">
-        <f t="shared" ref="C52:F52" si="34">+C31/C30</f>
+        <f t="shared" ref="C52:F52" si="37">+C31/C30</f>
         <v>0.2936337625178827</v>
       </c>
       <c r="D52" s="27">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0.2547284400485858</v>
       </c>
       <c r="E52" s="27">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0.29063379338067802</v>
       </c>
       <c r="F52" s="27">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0.26831356243120946</v>
       </c>
       <c r="G52" s="27">
@@ -6495,37 +6764,43 @@
         <v>0.22973467520585544</v>
       </c>
       <c r="H52" s="27">
-        <f t="shared" ref="H52:I52" si="35">+H31/H30</f>
+        <f t="shared" ref="H52:I52" si="38">+H31/H30</f>
         <v>0.21763739273324814</v>
       </c>
       <c r="I52" s="27">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.27327300421109219</v>
       </c>
-      <c r="J52" s="27"/>
+      <c r="J52" s="27">
+        <f t="shared" ref="J52" si="39">+J31/J30</f>
+        <v>0.26582401555663587</v>
+      </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="27">
-        <f t="shared" ref="M52:P52" si="36">+M31/M30</f>
+        <f t="shared" ref="M52:P52" si="40">+M31/M30</f>
         <v>0</v>
       </c>
       <c r="N52" s="27">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0.26877224199288258</v>
       </c>
       <c r="O52" s="27">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0.27388815499779834</v>
       </c>
       <c r="P52" s="27">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0.27896419437340153</v>
       </c>
       <c r="Q52" s="27">
-        <f t="shared" ref="Q52" si="37">+Q31/Q30</f>
+        <f t="shared" ref="Q52:R52" si="41">+Q31/Q30</f>
         <v>0.22367940047523305</v>
       </c>
-      <c r="R52" s="4"/>
+      <c r="R52" s="27">
+        <f t="shared" si="41"/>
+        <v>0.26970064347663902</v>
+      </c>
       <c r="S52" s="4"/>
       <c r="T52" s="4"/>
       <c r="U52" s="4"/>

--- a/2020.HK.xlsx
+++ b/2020.HK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13C1D0D-6D4B-4D61-A784-457070D150FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AE3255-1257-41D6-B6B1-5F451925B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{A24C8550-AABC-4E33-81F8-E1B227287154}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{A24C8550-AABC-4E33-81F8-E1B227287154}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2018,7 +2018,7 @@
         <v>16390</v>
       </c>
       <c r="J11" s="3">
-        <f>+R11-I11</f>
+        <f t="shared" ref="J11:J21" si="3">+R11-I11</f>
         <v>15059</v>
       </c>
       <c r="K11" s="3"/>
@@ -2110,28 +2110,28 @@
         <v>14036</v>
       </c>
       <c r="D12" s="3">
-        <f t="shared" ref="D12:D33" si="3">+O12-C12</f>
+        <f t="shared" ref="D12:D33" si="4">+O12-C12</f>
         <v>15487</v>
       </c>
       <c r="E12" s="4">
         <v>16313</v>
       </c>
       <c r="F12" s="4">
-        <f t="shared" ref="F12:F33" si="4">+P12-E12</f>
+        <f t="shared" ref="F12:F33" si="5">+P12-E12</f>
         <v>18754</v>
       </c>
       <c r="G12" s="4">
         <v>18082</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" ref="H12:H33" si="5">+Q12-G12</f>
+        <f t="shared" ref="H12:H33" si="6">+Q12-G12</f>
         <v>21303</v>
       </c>
       <c r="I12" s="4">
         <v>20886</v>
       </c>
       <c r="J12" s="3">
-        <f>+R12-I12</f>
+        <f t="shared" si="3"/>
         <v>24928</v>
       </c>
       <c r="K12" s="4"/>
@@ -2223,28 +2223,28 @@
         <v>818</v>
       </c>
       <c r="D13" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>839</v>
       </c>
       <c r="E13" s="4">
         <v>925</v>
       </c>
       <c r="F13" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1032</v>
       </c>
       <c r="G13" s="4">
         <v>1018</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1221</v>
       </c>
       <c r="I13" s="4">
         <v>1268</v>
       </c>
       <c r="J13" s="3">
-        <f>+R13-I13</f>
+        <f t="shared" si="3"/>
         <v>1638</v>
       </c>
       <c r="K13" s="4"/>
@@ -2336,28 +2336,28 @@
         <v>13360</v>
       </c>
       <c r="D14" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14363</v>
       </c>
       <c r="E14" s="4">
         <v>14170</v>
       </c>
       <c r="F14" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16136</v>
       </c>
       <c r="G14" s="4">
         <v>16077</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>17445</v>
       </c>
       <c r="I14" s="4">
         <v>16950</v>
       </c>
       <c r="J14" s="3">
-        <f>+R14-I14</f>
+        <f t="shared" si="3"/>
         <v>17804</v>
       </c>
       <c r="K14" s="4"/>
@@ -2449,28 +2449,28 @@
         <v>10777</v>
       </c>
       <c r="D15" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10746</v>
       </c>
       <c r="E15" s="4">
         <v>12229</v>
       </c>
       <c r="F15" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12874</v>
       </c>
       <c r="G15" s="4">
         <v>13056</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>13570</v>
       </c>
       <c r="I15" s="4">
         <v>14182</v>
       </c>
       <c r="J15" s="3">
-        <f>+R15-I15</f>
+        <f t="shared" si="3"/>
         <v>14287</v>
       </c>
       <c r="K15" s="4"/>
@@ -2562,28 +2562,28 @@
         <v>1828</v>
       </c>
       <c r="D16" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2577</v>
       </c>
       <c r="E16" s="4">
         <v>3246</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3701</v>
       </c>
       <c r="G16" s="4">
         <v>4602</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6076</v>
       </c>
       <c r="I16" s="4">
         <v>7412</v>
       </c>
       <c r="J16" s="3">
-        <f>+R16-I16</f>
+        <f t="shared" si="3"/>
         <v>9584</v>
       </c>
       <c r="K16" s="4"/>
@@ -2675,28 +2675,28 @@
         <v>6640</v>
       </c>
       <c r="D17" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7047</v>
       </c>
       <c r="E17" s="4">
         <v>8085</v>
       </c>
       <c r="F17" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8920</v>
       </c>
       <c r="G17" s="4">
         <v>8937</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9301</v>
       </c>
       <c r="I17" s="4">
         <v>9413</v>
       </c>
       <c r="J17" s="3">
-        <f>+R17-I17</f>
+        <f t="shared" si="3"/>
         <v>9292</v>
       </c>
       <c r="K17" s="4"/>
@@ -2789,28 +2789,28 @@
         <v>4569</v>
       </c>
       <c r="D18" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4108</v>
       </c>
       <c r="E18" s="4">
         <v>4635</v>
       </c>
       <c r="F18" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5296</v>
       </c>
       <c r="G18" s="4">
         <v>5567</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6418</v>
       </c>
       <c r="I18" s="4">
         <v>6131</v>
       </c>
       <c r="J18" s="3">
-        <f>+R18-I18</f>
+        <f t="shared" si="3"/>
         <v>6732</v>
       </c>
       <c r="K18" s="4"/>
@@ -2902,28 +2902,28 @@
         <v>2151</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2208</v>
       </c>
       <c r="E19" s="4">
         <v>1450</v>
       </c>
       <c r="F19" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1920</v>
       </c>
       <c r="G19" s="4">
         <v>1573</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1726</v>
       </c>
       <c r="I19" s="4">
         <v>1406</v>
       </c>
       <c r="J19" s="3">
-        <f>+R19-I19</f>
+        <f t="shared" si="3"/>
         <v>1780</v>
       </c>
       <c r="K19" s="4"/>
@@ -3022,21 +3022,21 @@
         <v>29645</v>
       </c>
       <c r="F20" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>32711</v>
       </c>
       <c r="G20" s="25">
         <v>33735</v>
       </c>
       <c r="H20" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>37091</v>
       </c>
       <c r="I20" s="25">
         <v>38544</v>
       </c>
       <c r="J20" s="24">
-        <f>+R20-I20</f>
+        <f t="shared" si="3"/>
         <v>41675</v>
       </c>
       <c r="K20" s="25"/>
@@ -3130,28 +3130,28 @@
         <v>9856</v>
       </c>
       <c r="D21" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>11477</v>
       </c>
       <c r="E21" s="4">
         <v>10890</v>
       </c>
       <c r="F21" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12438</v>
       </c>
       <c r="G21" s="4">
         <v>12117</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14677</v>
       </c>
       <c r="I21" s="4">
         <v>14119</v>
       </c>
       <c r="J21" s="3">
-        <f>+R21-I21</f>
+        <f t="shared" si="3"/>
         <v>16366</v>
       </c>
       <c r="K21" s="4"/>
@@ -3240,11 +3240,11 @@
         <v>44</v>
       </c>
       <c r="C22" s="4">
-        <f t="shared" ref="C22:D22" si="6">+C20-C21</f>
+        <f t="shared" ref="C22:D22" si="7">+C20-C21</f>
         <v>16109</v>
       </c>
       <c r="D22" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>16209</v>
       </c>
       <c r="E22" s="4">
@@ -3252,44 +3252,44 @@
         <v>18755</v>
       </c>
       <c r="F22" s="4">
-        <f t="shared" ref="F22:J22" si="7">+F20-F21</f>
+        <f t="shared" ref="F22:J22" si="8">+F20-F21</f>
         <v>20273</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>21618</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>22414</v>
       </c>
       <c r="I22" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>24425</v>
       </c>
       <c r="J22" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>25309</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4">
-        <f t="shared" ref="L22:P22" si="8">+L20-L21</f>
+        <f t="shared" ref="L22:P22" si="9">+L20-L21</f>
         <v>0</v>
       </c>
       <c r="M22" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>35512</v>
       </c>
       <c r="N22" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>30404</v>
       </c>
       <c r="O22" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>32318</v>
       </c>
       <c r="P22" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>39028</v>
       </c>
       <c r="Q22" s="4">
@@ -3371,21 +3371,21 @@
         <v>821</v>
       </c>
       <c r="D23" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1307</v>
       </c>
       <c r="E23" s="4">
         <v>637</v>
       </c>
       <c r="F23" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1068</v>
       </c>
       <c r="G23" s="4">
         <v>809</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1599</v>
       </c>
       <c r="I23" s="4">
@@ -3484,21 +3484,21 @@
         <v>9437</v>
       </c>
       <c r="D24" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10192</v>
       </c>
       <c r="E24" s="4">
         <v>10074</v>
       </c>
       <c r="F24" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11599</v>
       </c>
       <c r="G24" s="4">
         <v>11796</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>13851</v>
       </c>
       <c r="I24" s="4">
@@ -3597,21 +3597,21 @@
         <v>1701</v>
       </c>
       <c r="D25" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1886</v>
       </c>
       <c r="E25" s="4">
         <v>1695</v>
       </c>
       <c r="F25" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1998</v>
       </c>
       <c r="G25" s="4">
         <v>1971</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2227</v>
       </c>
       <c r="I25" s="4">
@@ -3707,19 +3707,19 @@
         <v>48</v>
       </c>
       <c r="C26" s="4">
-        <f t="shared" ref="C26:F26" si="9">+C22+C23-SUM(C24:C25)</f>
+        <f t="shared" ref="C26:F26" si="10">+C22+C23-SUM(C24:C25)</f>
         <v>5792</v>
       </c>
       <c r="D26" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5438</v>
       </c>
       <c r="E26" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7623</v>
       </c>
       <c r="F26" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7744</v>
       </c>
       <c r="G26" s="4">
@@ -3727,44 +3727,44 @@
         <v>8660</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" ref="H26:R26" si="10">+H22+H23-SUM(H24:H25)</f>
+        <f t="shared" ref="H26:R26" si="11">+H22+H23-SUM(H24:H25)</f>
         <v>7935</v>
       </c>
       <c r="I26" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10131</v>
       </c>
       <c r="J26" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8960</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M26" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>35512</v>
       </c>
       <c r="N26" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10989</v>
       </c>
       <c r="O26" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>11230</v>
       </c>
       <c r="P26" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>15367</v>
       </c>
       <c r="Q26" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>16595</v>
       </c>
       <c r="R26" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>19091</v>
       </c>
       <c r="S26" s="4"/>
@@ -3838,21 +3838,21 @@
         <v>-22</v>
       </c>
       <c r="D27" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>119</v>
       </c>
       <c r="E27" s="4">
         <v>356</v>
       </c>
       <c r="F27" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>635</v>
       </c>
       <c r="G27" s="4">
         <v>710</v>
       </c>
       <c r="H27" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>678</v>
       </c>
       <c r="I27" s="4">
@@ -3951,21 +3951,21 @@
         <v>-178</v>
       </c>
       <c r="D28" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>206</v>
       </c>
       <c r="E28" s="4">
         <v>-516</v>
       </c>
       <c r="F28" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-202</v>
       </c>
       <c r="G28" s="4">
         <v>-19</v>
       </c>
       <c r="H28" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>217</v>
       </c>
       <c r="I28" s="4">
@@ -4064,21 +4064,21 @@
         <v>0</v>
       </c>
       <c r="D29" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
       </c>
       <c r="F29" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G29" s="4">
         <v>1579</v>
       </c>
       <c r="H29" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2124</v>
       </c>
       <c r="I29" s="4">
@@ -4175,19 +4175,19 @@
         <v>52</v>
       </c>
       <c r="C30" s="4">
-        <f t="shared" ref="C30:F30" si="11">+C26+SUM(C27:C29)</f>
+        <f t="shared" ref="C30:F30" si="12">+C26+SUM(C27:C29)</f>
         <v>5592</v>
       </c>
       <c r="D30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5763</v>
       </c>
       <c r="E30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7463</v>
       </c>
       <c r="F30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8177</v>
       </c>
       <c r="G30" s="4">
@@ -4195,44 +4195,44 @@
         <v>10930</v>
       </c>
       <c r="H30" s="4">
-        <f t="shared" ref="H30:R30" si="12">+H26+SUM(H27:H29)</f>
+        <f t="shared" ref="H30:R30" si="13">+H26+SUM(H27:H29)</f>
         <v>10954</v>
       </c>
       <c r="I30" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11161</v>
       </c>
       <c r="J30" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>10285</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M30" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>35512</v>
       </c>
       <c r="N30" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11240</v>
       </c>
       <c r="O30" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11355</v>
       </c>
       <c r="P30" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15640</v>
       </c>
       <c r="Q30" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>21884</v>
       </c>
       <c r="R30" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>21446</v>
       </c>
       <c r="S30" s="4"/>
@@ -4306,21 +4306,21 @@
         <v>1642</v>
       </c>
       <c r="D31" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1468</v>
       </c>
       <c r="E31" s="4">
         <v>2169</v>
       </c>
       <c r="F31" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2194</v>
       </c>
       <c r="G31" s="4">
         <v>2511</v>
       </c>
       <c r="H31" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2384</v>
       </c>
       <c r="I31" s="4">
@@ -4416,19 +4416,19 @@
         <v>54</v>
       </c>
       <c r="C32" s="4">
-        <f t="shared" ref="C32:F32" si="13">+C30-C31</f>
+        <f t="shared" ref="C32:F32" si="14">+C30-C31</f>
         <v>3950</v>
       </c>
       <c r="D32" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4295</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5294</v>
       </c>
       <c r="F32" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5983</v>
       </c>
       <c r="G32" s="4">
@@ -4436,36 +4436,36 @@
         <v>8419</v>
       </c>
       <c r="H32" s="4">
-        <f t="shared" ref="H32:J32" si="14">+H30-H31</f>
+        <f t="shared" ref="H32:J32" si="15">+H30-H31</f>
         <v>8570</v>
       </c>
       <c r="I32" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8111</v>
       </c>
       <c r="J32" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7551</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4">
-        <f t="shared" ref="L32:P32" si="15">+L30-L31</f>
+        <f t="shared" ref="L32:P32" si="16">+L30-L31</f>
         <v>0</v>
       </c>
       <c r="M32" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>35512</v>
       </c>
       <c r="N32" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8219</v>
       </c>
       <c r="O32" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8245</v>
       </c>
       <c r="P32" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>11277</v>
       </c>
       <c r="Q32" s="4">
@@ -4547,21 +4547,21 @@
         <v>362</v>
       </c>
       <c r="D33" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>293</v>
       </c>
       <c r="E33" s="4">
         <v>546</v>
       </c>
       <c r="F33" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>495</v>
       </c>
       <c r="G33" s="4">
         <v>698</v>
       </c>
       <c r="H33" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>695</v>
       </c>
       <c r="I33" s="4">
@@ -4657,19 +4657,19 @@
         <v>56</v>
       </c>
       <c r="C34" s="4">
-        <f t="shared" ref="C34:F34" si="16">+C32-C33</f>
+        <f t="shared" ref="C34:F34" si="17">+C32-C33</f>
         <v>3588</v>
       </c>
       <c r="D34" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4002</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4748</v>
       </c>
       <c r="F34" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>5488</v>
       </c>
       <c r="G34" s="4">
@@ -4677,36 +4677,36 @@
         <v>7721</v>
       </c>
       <c r="H34" s="4">
-        <f t="shared" ref="H34:J34" si="17">+H32-H33</f>
+        <f t="shared" ref="H34:J34" si="18">+H32-H33</f>
         <v>7875</v>
       </c>
       <c r="I34" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>7031</v>
       </c>
       <c r="J34" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>6557</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4">
-        <f t="shared" ref="L34:P34" si="18">+L32-L33</f>
+        <f t="shared" ref="L34:P34" si="19">+L32-L33</f>
         <v>0</v>
       </c>
       <c r="M34" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>35512</v>
       </c>
       <c r="N34" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7720</v>
       </c>
       <c r="O34" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7590</v>
       </c>
       <c r="P34" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10236</v>
       </c>
       <c r="Q34" s="4">
@@ -4865,11 +4865,11 @@
         <v>57</v>
       </c>
       <c r="C36" s="26">
-        <f t="shared" ref="C36:D36" si="19">+C34/C37</f>
+        <f t="shared" ref="C36:D36" si="20">+C34/C37</f>
         <v>1.3330291787752626</v>
       </c>
       <c r="D36" s="26">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.4864901004662274</v>
       </c>
       <c r="E36" s="26">
@@ -4877,44 +4877,44 @@
         <v>1.7353820197902265</v>
       </c>
       <c r="F36" s="26">
-        <f t="shared" ref="F36:J36" si="20">+F34/F37</f>
+        <f t="shared" ref="F36:J36" si="21">+F34/F37</f>
         <v>1.9778394050624473</v>
       </c>
       <c r="G36" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.7461456684273626</v>
       </c>
       <c r="H36" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.8041107016614935</v>
       </c>
       <c r="I36" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.5281563480060609</v>
       </c>
       <c r="J36" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.3582666290705907</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="26" t="e">
-        <f t="shared" ref="L36:P36" si="21">+L34/L37</f>
+        <f t="shared" ref="L36:P36" si="22">+L34/L37</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M36" s="26" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N36" s="26">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2.8695321844796968</v>
       </c>
       <c r="O36" s="26">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2.8192053629531899</v>
       </c>
       <c r="P36" s="26">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3.6889876367017513</v>
       </c>
       <c r="Q36" s="26">
@@ -5187,53 +5187,53 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="27">
-        <f>+E9/C9-1</f>
+        <f t="shared" ref="E39:J39" si="23">+E9/C9-1</f>
         <v>2.927713964936518E-2</v>
       </c>
       <c r="F39" s="27">
-        <f>+F9/D9-1</f>
+        <f t="shared" si="23"/>
         <v>1.8008208392662706E-2</v>
       </c>
       <c r="G39" s="27">
-        <f>+G9/E9-1</f>
+        <f t="shared" si="23"/>
         <v>2.7185769424399986E-2</v>
       </c>
       <c r="H39" s="27">
-        <f>+H9/F9-1</f>
+        <f t="shared" si="23"/>
         <v>2.3778180023037665E-2</v>
       </c>
       <c r="I39" s="27">
-        <f>+I9/G9-1</f>
+        <f t="shared" si="23"/>
         <v>1.7235745793171109E-2</v>
       </c>
       <c r="J39" s="27">
-        <f>+J9/H9-1</f>
+        <f t="shared" si="23"/>
         <v>-8.1170135819336187E-3</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="27" t="e">
-        <f>+M9/L9-1</f>
+        <f t="shared" ref="M39:R39" si="24">+M9/L9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N39" s="27" t="e">
-        <f>+N9/M9-1</f>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O39" s="27">
-        <f>+O9/N9-1</f>
+        <f t="shared" si="24"/>
         <v>1.2294386976428706E-2</v>
       </c>
       <c r="P39" s="27">
-        <f>+P9/O9-1</f>
+        <f t="shared" si="24"/>
         <v>1.8008208392662706E-2</v>
       </c>
       <c r="Q39" s="27">
-        <f>+Q9/P9-1</f>
+        <f t="shared" si="24"/>
         <v>1.991114036531183E-2</v>
       </c>
       <c r="R39" s="27">
-        <f>+R9/Q9-1</f>
+        <f t="shared" si="24"/>
         <v>-4.3562439496611649E-3</v>
       </c>
       <c r="S39" s="4"/>
@@ -5306,11 +5306,11 @@
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="27">
-        <f t="shared" ref="E40:F49" si="22">+E11/C11-1</f>
+        <f t="shared" ref="E40:F49" si="25">+E11/C11-1</f>
         <v>0.11664116641166422</v>
       </c>
       <c r="F40" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.13776408450704225</v>
       </c>
       <c r="G40" s="27">
@@ -5318,33 +5318,33 @@
         <v>0.17957604578060771</v>
       </c>
       <c r="H40" s="27">
-        <f t="shared" ref="H40:J49" si="23">+H11/F11-1</f>
+        <f t="shared" ref="H40:J49" si="26">+H11/F11-1</f>
         <v>0.12704061895551266</v>
       </c>
       <c r="I40" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.11991800478305437</v>
       </c>
       <c r="J40" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>3.3774970824466344E-2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="27" t="e">
-        <f t="shared" ref="M40:P49" si="24">+M11/L11-1</f>
+        <f t="shared" ref="M40:P49" si="27">+M11/L11-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N40" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O40" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.17409478029155134</v>
       </c>
       <c r="P40" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.12731965644608612</v>
       </c>
       <c r="Q40" s="27">
@@ -5425,53 +5425,53 @@
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.16222570532915359</v>
       </c>
       <c r="F41" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.21095112029444052</v>
       </c>
       <c r="G41" s="27">
-        <f t="shared" ref="G41:G49" si="25">+G12/E12-1</f>
+        <f t="shared" ref="G41:G49" si="28">+G12/E12-1</f>
         <v>0.1084411205786795</v>
       </c>
       <c r="H41" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.13591767089687523</v>
       </c>
       <c r="I41" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.15507134166574499</v>
       </c>
       <c r="J41" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.17016382669107633</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
       <c r="M41" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N41" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O41" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>3.111902766135799E-2</v>
       </c>
       <c r="P41" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.18778579412661323</v>
       </c>
       <c r="Q41" s="27">
-        <f t="shared" ref="Q41:R49" si="26">+Q12/P12-1</f>
+        <f t="shared" ref="Q41:R49" si="29">+Q12/P12-1</f>
         <v>0.12313571163772208</v>
       </c>
       <c r="R41" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0.16323473403580047</v>
       </c>
       <c r="S41" s="4"/>
@@ -5544,53 +5544,53 @@
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.13080684596577008</v>
       </c>
       <c r="F42" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.23003575685339683</v>
       </c>
       <c r="G42" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0.10054054054054062</v>
       </c>
       <c r="H42" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.18313953488372103</v>
       </c>
       <c r="I42" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.24557956777996082</v>
       </c>
       <c r="J42" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.34152334152334163</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N42" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O42" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>6.4226075786769421E-2</v>
       </c>
       <c r="P42" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.18105009052504517</v>
       </c>
       <c r="Q42" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0.14409810935104761</v>
       </c>
       <c r="R42" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0.29790084859312183</v>
       </c>
       <c r="S42" s="4"/>
@@ -5663,53 +5663,53 @@
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>6.062874251497008E-2</v>
       </c>
       <c r="F43" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.12344217781800459</v>
       </c>
       <c r="G43" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0.13458009880028232</v>
       </c>
       <c r="H43" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>8.1122954883490417E-2</v>
       </c>
       <c r="I43" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>5.4301175592461171E-2</v>
       </c>
       <c r="J43" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>2.0578962453424943E-2</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N43" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O43" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.15454772613693146</v>
       </c>
       <c r="P43" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>9.3171734660751016E-2</v>
       </c>
       <c r="Q43" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0.1061176004751534</v>
       </c>
       <c r="R43" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>3.6751983771851293E-2</v>
       </c>
       <c r="S43" s="4"/>
@@ -5782,53 +5782,53 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.134731372367078</v>
       </c>
       <c r="F44" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.19802717290154481</v>
       </c>
       <c r="G44" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>6.7626134598086418E-2</v>
       </c>
       <c r="H44" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>5.4062451452540072E-2</v>
       </c>
       <c r="I44" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>8.6243872549019551E-2</v>
       </c>
       <c r="J44" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>5.2837140751658129E-2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N44" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O44" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>-1.3701768857116714E-2</v>
       </c>
       <c r="P44" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.16633368954142091</v>
       </c>
       <c r="Q44" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>6.0670039437517476E-2</v>
       </c>
       <c r="R44" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>6.9218057537745015E-2</v>
       </c>
       <c r="S44" s="4"/>
@@ -5901,53 +5901,53 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.775711159737418</v>
       </c>
       <c r="F45" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.43616608459448969</v>
       </c>
       <c r="G45" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0.41774491682070236</v>
       </c>
       <c r="H45" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.64171845447176445</v>
       </c>
       <c r="I45" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.61060408518035647</v>
       </c>
       <c r="J45" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.57735352205398294</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N45" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O45" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.26073268460217514</v>
       </c>
       <c r="P45" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.57707150964812715</v>
       </c>
       <c r="Q45" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0.53706635957967475</v>
       </c>
       <c r="R45" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0.59168383592433038</v>
       </c>
       <c r="S45" s="4"/>
@@ -6020,53 +6020,53 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.21762048192771077</v>
       </c>
       <c r="F46" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.26578685965659155</v>
       </c>
       <c r="G46" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0.10538033395176249</v>
       </c>
       <c r="H46" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>4.2713004484304928E-2</v>
       </c>
       <c r="I46" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>5.3261720935436907E-2</v>
       </c>
       <c r="J46" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-9.6763788839904219E-4</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N46" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O46" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.60007014262333414</v>
       </c>
       <c r="P46" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.24241981442244476</v>
       </c>
       <c r="Q46" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>7.2508085857100779E-2</v>
       </c>
       <c r="R46" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>2.5605877837482138E-2</v>
       </c>
       <c r="S46" s="4"/>
@@ -6139,53 +6139,53 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>1.4445173998686833E-2</v>
       </c>
       <c r="F47" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.28919182083739048</v>
       </c>
       <c r="G47" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0.20107874865156417</v>
       </c>
       <c r="H47" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.2118580060422961</v>
       </c>
       <c r="I47" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.10131129872462719</v>
       </c>
       <c r="J47" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>4.8924898722343402E-2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N47" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O47" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>5.5467704658800576E-2</v>
       </c>
       <c r="P47" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.14451999539011173</v>
       </c>
       <c r="Q47" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0.2068271070385661</v>
       </c>
       <c r="R47" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>7.3258239465999075E-2</v>
       </c>
       <c r="S47" s="4"/>
@@ -6258,53 +6258,53 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>-0.32589493258949331</v>
       </c>
       <c r="F48" s="27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>-0.13043478260869568</v>
       </c>
       <c r="G48" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>8.4827586206896566E-2</v>
       </c>
       <c r="H48" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-0.1010416666666667</v>
       </c>
       <c r="I48" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-0.10616656071201525</v>
       </c>
       <c r="J48" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>3.1286210892236488E-2</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N48" s="27" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O48" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>-0.39767859610335776</v>
       </c>
       <c r="P48" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>-0.22688690066529016</v>
       </c>
       <c r="Q48" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-2.1068249258160199E-2</v>
       </c>
       <c r="R48" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-3.4252803879963656E-2</v>
       </c>
       <c r="S48" s="4"/>
@@ -6377,53 +6377,53 @@
       <c r="C49" s="24"/>
       <c r="D49" s="24"/>
       <c r="E49" s="28">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.14172925091469279</v>
       </c>
       <c r="F49" s="28">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.18149967492595542</v>
       </c>
       <c r="G49" s="28">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0.13796593017372238</v>
       </c>
       <c r="H49" s="28">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.13389991134480761</v>
       </c>
       <c r="I49" s="28">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.14255224544241885</v>
       </c>
       <c r="J49" s="28">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.12358793238251864</v>
       </c>
       <c r="K49" s="25"/>
       <c r="L49" s="25"/>
       <c r="M49" s="28" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N49" s="28">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.38905158819553964</v>
       </c>
       <c r="O49" s="28">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>8.7637852740836797E-2</v>
       </c>
       <c r="P49" s="28">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.16225233453244114</v>
       </c>
       <c r="Q49" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0.13583295913785354</v>
       </c>
       <c r="R49" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0.13262078897579976</v>
       </c>
       <c r="S49" s="25"/>
@@ -6494,19 +6494,19 @@
         <v>69</v>
       </c>
       <c r="C50" s="27">
-        <f t="shared" ref="C50:F50" si="27">+C22/C20</f>
+        <f t="shared" ref="C50:F50" si="30">+C22/C20</f>
         <v>0.62041209320238788</v>
       </c>
       <c r="D50" s="27">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.58545835440294736</v>
       </c>
       <c r="E50" s="27">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.63265306122448983</v>
       </c>
       <c r="F50" s="27">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.61976093668796428</v>
       </c>
       <c r="G50" s="27">
@@ -6514,41 +6514,41 @@
         <v>0.6408181413961761</v>
       </c>
       <c r="H50" s="27">
-        <f t="shared" ref="H50:I50" si="28">+H22/H20</f>
+        <f t="shared" ref="H50:I50" si="31">+H22/H20</f>
         <v>0.60429753848642531</v>
       </c>
       <c r="I50" s="27">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0.63369136571191365</v>
       </c>
       <c r="J50" s="27">
-        <f t="shared" ref="J50" si="29">+J22/J20</f>
+        <f t="shared" ref="J50" si="32">+J22/J20</f>
         <v>0.6072945410917816</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="27">
-        <f t="shared" ref="M50:P50" si="30">+M22/M20</f>
+        <f t="shared" ref="M50:P50" si="33">+M22/M20</f>
         <v>1</v>
       </c>
       <c r="N50" s="27">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0.61636393123580924</v>
       </c>
       <c r="O50" s="27">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0.6023746062515144</v>
       </c>
       <c r="P50" s="27">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0.62589005067675929</v>
       </c>
       <c r="Q50" s="27">
-        <f t="shared" ref="Q50:R50" si="31">+Q22/Q20</f>
+        <f t="shared" ref="Q50:R50" si="34">+Q22/Q20</f>
         <v>0.62169259876316607</v>
       </c>
       <c r="R50" s="27">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0.61997781074309077</v>
       </c>
       <c r="S50" s="4"/>
@@ -6619,19 +6619,19 @@
         <v>70</v>
       </c>
       <c r="C51" s="27">
-        <f t="shared" ref="C51:F51" si="32">+C26/C20</f>
+        <f t="shared" ref="C51:F51" si="35">+C26/C20</f>
         <v>0.22306951665703831</v>
       </c>
       <c r="D51" s="27">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0.19641696164126274</v>
       </c>
       <c r="E51" s="27">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0.25714285714285712</v>
       </c>
       <c r="F51" s="27">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0.23673993457858214</v>
       </c>
       <c r="G51" s="27">
@@ -6639,41 +6639,41 @@
         <v>0.25670668445234918</v>
       </c>
       <c r="H51" s="27">
-        <f t="shared" ref="H51:I51" si="33">+H26/H20</f>
+        <f t="shared" ref="H51:I51" si="36">+H26/H20</f>
         <v>0.21393329918309023</v>
       </c>
       <c r="I51" s="27">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.26284246575342468</v>
       </c>
       <c r="J51" s="27">
-        <f t="shared" ref="J51" si="34">+J26/J20</f>
+        <f t="shared" ref="J51" si="37">+J26/J20</f>
         <v>0.21499700059988003</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="27">
-        <f t="shared" ref="M51:P51" si="35">+M26/M20</f>
+        <f t="shared" ref="M51:P51" si="38">+M26/M20</f>
         <v>1</v>
       </c>
       <c r="N51" s="27">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.22277408368472268</v>
       </c>
       <c r="O51" s="27">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.2093157629867104</v>
       </c>
       <c r="P51" s="27">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.24643979729296298</v>
       </c>
       <c r="Q51" s="27">
-        <f t="shared" ref="Q51:R51" si="36">+Q26/Q20</f>
+        <f t="shared" ref="Q51:R51" si="39">+Q26/Q20</f>
         <v>0.23430661056674101</v>
       </c>
       <c r="R51" s="27">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.2379860132886224</v>
       </c>
       <c r="S51" s="4"/>
@@ -6744,19 +6744,19 @@
         <v>71</v>
       </c>
       <c r="C52" s="27">
-        <f t="shared" ref="C52:F52" si="37">+C31/C30</f>
+        <f t="shared" ref="C52:F52" si="40">+C31/C30</f>
         <v>0.2936337625178827</v>
       </c>
       <c r="D52" s="27">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.2547284400485858</v>
       </c>
       <c r="E52" s="27">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.29063379338067802</v>
       </c>
       <c r="F52" s="27">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.26831356243120946</v>
       </c>
       <c r="G52" s="27">
@@ -6764,41 +6764,41 @@
         <v>0.22973467520585544</v>
       </c>
       <c r="H52" s="27">
-        <f t="shared" ref="H52:I52" si="38">+H31/H30</f>
+        <f t="shared" ref="H52:I52" si="41">+H31/H30</f>
         <v>0.21763739273324814</v>
       </c>
       <c r="I52" s="27">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>0.27327300421109219</v>
       </c>
       <c r="J52" s="27">
-        <f t="shared" ref="J52" si="39">+J31/J30</f>
+        <f t="shared" ref="J52" si="42">+J31/J30</f>
         <v>0.26582401555663587</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="27">
-        <f t="shared" ref="M52:P52" si="40">+M31/M30</f>
+        <f t="shared" ref="M52:P52" si="43">+M31/M30</f>
         <v>0</v>
       </c>
       <c r="N52" s="27">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.26877224199288258</v>
       </c>
       <c r="O52" s="27">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.27388815499779834</v>
       </c>
       <c r="P52" s="27">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.27896419437340153</v>
       </c>
       <c r="Q52" s="27">
-        <f t="shared" ref="Q52:R52" si="41">+Q31/Q30</f>
+        <f t="shared" ref="Q52:R52" si="44">+Q31/Q30</f>
         <v>0.22367940047523305</v>
       </c>
       <c r="R52" s="27">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.26970064347663902</v>
       </c>
       <c r="S52" s="4"/>
